--- a/latest.xlsx
+++ b/latest.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T14:22:27+08:00</t>
+          <t>2026-08-07T14:44:24+08:00</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
     </row>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>高级技师</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>高级技师</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>高级技师</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>高级技师</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>高级技师</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -14360,7 +14360,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>高级技师</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
@@ -14515,7 +14515,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>高级技师</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>高级技师</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -16156,7 +16156,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>高级技师</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
@@ -16895,7 +16895,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
@@ -17046,7 +17046,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
@@ -17193,7 +17193,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
@@ -18385,7 +18385,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>高级技师</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
@@ -18540,7 +18540,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -20022,7 +20022,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -20773,7 +20773,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -21969,7 +21969,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -22267,7 +22267,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
@@ -33578,7 +33578,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
@@ -34810,7 +34810,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>高级技师</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
@@ -34965,7 +34965,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>高级技师</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>高级技师</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
@@ -36106,7 +36106,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>技师及高级技师</t>
+          <t>技师</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
@@ -36682,16 +36682,16 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="E7" s="5" t="n">
         <v>59</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>60</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -36719,13 +36719,13 @@
         <v>19</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
     </row>
@@ -36789,7 +36789,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
     </row>
@@ -36887,7 +36887,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
     </row>
@@ -36917,7 +36917,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
     </row>
@@ -36947,7 +36947,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
     </row>
@@ -36977,7 +36977,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
@@ -37007,7 +37007,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
     </row>
@@ -37071,7 +37071,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
     </row>
@@ -37101,7 +37101,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
     </row>
@@ -37165,7 +37165,7 @@
         <v>3</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
     </row>
@@ -37229,7 +37229,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
     </row>
@@ -37259,7 +37259,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
     </row>
@@ -38000,16 +38000,16 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
     </row>
